--- a/Config/Datas/micro_plot.xlsx
+++ b/Config/Datas/micro_plot.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17655" activeTab="1"/>
+    <workbookView windowHeight="17655"/>
   </bookViews>
   <sheets>
     <sheet name="micro_plot_def" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="55">
   <si>
     <t>##var</t>
   </si>
@@ -46,6 +46,9 @@
     <t>consume_on</t>
   </si>
   <si>
+    <t>reward_items</t>
+  </si>
+  <si>
     <t>##type</t>
   </si>
   <si>
@@ -61,12 +64,18 @@
     <t>EMicroPlotConsumeOn</t>
   </si>
   <si>
+    <t>(map#sep=,|),string,int</t>
+  </si>
+  <si>
     <t>##group</t>
   </si>
   <si>
     <t>c,s</t>
   </si>
   <si>
+    <t>c</t>
+  </si>
+  <si>
     <t>##</t>
   </si>
   <si>
@@ -82,12 +91,21 @@
     <t>完成后何时记为已消耗：SuccessOrAbort / SuccessOnly</t>
   </si>
   <si>
+    <t>奖励</t>
+  </si>
+  <si>
     <t>demo_micro_plot</t>
   </si>
   <si>
     <t>cornor_01_a|cornor_01_b</t>
   </si>
   <si>
+    <t>SuccessOrAbort</t>
+  </si>
+  <si>
+    <t>rumor_points,10</t>
+  </si>
+  <si>
     <t>map_id</t>
   </si>
   <si>
@@ -160,10 +178,22 @@
     <t>managed_uniqnames 下标</t>
   </si>
   <si>
-    <t>Log</t>
+    <t>NpcSpeak</t>
   </si>
   <si>
     <t>aaa</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>bbbbb</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>ccccc</t>
   </si>
 </sst>
 </file>
@@ -1126,15 +1156,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="4" outlineLevelCol="4"/>
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="4" outlineLevelCol="5"/>
   <cols>
     <col min="2" max="2" width="16.125" customWidth="1"/>
     <col min="3" max="3" width="14.75" customWidth="1"/>
     <col min="4" max="4" width="13.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:6">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1150,70 +1180,85 @@
       <c r="E1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:5">
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
+        <v>10</v>
+      </c>
+      <c r="F2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C3" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D3" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
+        <v>13</v>
+      </c>
+      <c r="F3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
       <c r="A4" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B4" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C4" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D4" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
+        <v>19</v>
+      </c>
+      <c r="F4" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
       <c r="B5" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C5" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="D5">
         <v>30</v>
       </c>
-      <c r="E5">
-        <v>0</v>
+      <c r="E5" t="s">
+        <v>23</v>
+      </c>
+      <c r="F5" t="s">
+        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -1240,108 +1285,108 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="D1" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="E1" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="F1" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="G1" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="H1" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G2" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="H2" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C3" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D3" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E3" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F3" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G3" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H3" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B4" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="C4" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D4" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="E4" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="F4" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="G4" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="H4" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
     </row>
     <row r="5" spans="1:8">
       <c r="B5" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="C5" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="D5">
         <v>1.02</v>
@@ -1350,7 +1395,7 @@
         <v>-22.66</v>
       </c>
       <c r="F5" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -1368,9 +1413,10 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="4" outlineLevelCol="6"/>
+  <dimension ref="A1:G7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="6" outlineLevelCol="6"/>
   <cols>
+    <col min="3" max="3" width="9.875" customWidth="1"/>
     <col min="4" max="4" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -1382,64 +1428,64 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="E1" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="F1" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="G1" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="C2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E2" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="F2" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="G2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C3" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="F4" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -1447,19 +1493,59 @@
         <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D5" s="1">
         <v>1</v>
       </c>
       <c r="E5" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="F5">
         <v>0</v>
       </c>
       <c r="G5" t="s">
-        <v>44</v>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="B6">
+        <v>2</v>
+      </c>
+      <c r="C6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="E6" t="s">
+        <v>49</v>
+      </c>
+      <c r="F6">
+        <v>1</v>
+      </c>
+      <c r="G6" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="B7">
+        <v>3</v>
+      </c>
+      <c r="C7" t="s">
+        <v>21</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="E7" t="s">
+        <v>49</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7" t="s">
+        <v>54</v>
       </c>
     </row>
   </sheetData>
